--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.1.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.1.xlsx
@@ -6251,7 +6251,7 @@
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】成果報酬（応募1件 6,000円）（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
+          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】成果報酬（応募1件 20,000円）（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
         </is>
       </c>
       <c r="N4" s="55"/>
@@ -6326,7 +6326,7 @@
         <v>178</v>
       </c>
       <c r="D8" s="33">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="G8" s="121" t="s">
         <v>162</v>
@@ -6389,7 +6389,7 @@
         <v>179</v>
       </c>
       <c r="D10" s="33">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="G10" s="124" t="s">
         <v>164</v>
